--- a/technology_surveys/012_equity_in_digital_access_survey--technology_surveys.xlsx
+++ b/technology_surveys/012_equity_in_digital_access_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what is the primary reason prophets and prophets are used in the bible</t>
+          <t>What is the primary reason you use the Bible?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what is the primary reason prophets and prophets are used in the bible</t>
+          <t>What are the goals of your organization?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what is the primary reason prophets and prophets are used in the bible</t>
+          <t>What type of equipment would you like to see your organization support?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4_goals</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what are the goals of the organization</t>
+          <t>Question 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5_goals</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what are the goals of the organization</t>
+          <t>What barriers do you face when accessing the internet?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6_equipment</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what type of equipment would you like to see the organization support</t>
+          <t>What type of internet access do you have?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7_equipment</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what type of equipment would you like to see the organization support</t>
+          <t>What type of device do you use to access the internet?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8_barriers</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what barriers do you face when accessing the internet</t>
+          <t>What is the current quality of your internet connection?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9_barriers</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what barriers do you face when accessing the internet</t>
+          <t>What is the current speed of your internet connection?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,343 +745,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_11_internet</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what type of internet access do you have</t>
+          <t>Do you have any further comments or suggestions?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>question_12_internet</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>what type of internet access do you have</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>question_13_devices</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>what type of device do you use to access the internet</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_14_devices</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>what type of device do you use to access the internet</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_15_quality</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>what is the current quality of your internet connection</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_16_quality</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>what is the current quality of your internet connection</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_17_speed</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>what is the current speed of your internet connection</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_18_speed</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>what is the current speed of your internet connection</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_19_barriers</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>what type of barrier do you face when using the internet</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_20_barriers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>what type of barrier do you face when using the internet</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_21_device</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>what type of device do you have for accessing the internet</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_22_device</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>what type of device do you have for accessing the internet</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_23_access</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what type of access do you have to the internet</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_24_access</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what type of access do you have to the internet</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_25_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>do you have any comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>personal_devotion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Personal Devotion</t>
         </is>
       </c>
     </row>
@@ -1148,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>study_and_research</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Study and Research</t>
         </is>
       </c>
     </row>
@@ -1165,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>spiritual_guidance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Spiritual Guidance</t>
         </is>
       </c>
     </row>
@@ -1182,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Financial Support</t>
         </is>
       </c>
     </row>
@@ -1216,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>resource_sharing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Resource Sharing</t>
         </is>
       </c>
     </row>
@@ -1233,828 +911,352 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>community_building</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Community Building</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_goals_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_4_goals_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_4_goals_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>internet_connection</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Internet Connection</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_5_goals_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>mobile_device</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Mobile Device</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_goals_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_5_goals_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_6_equipment_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>internet_connection</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Internet Connection</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_6_equipment_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>mobile_device</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Mobile Device</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_6_equipment_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_equipment_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>affordability</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Affordability</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_7_equipment_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>accessibility</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Accessibility</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_7_equipment_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>technical_issues</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Technical Issues</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_8_barriers_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_8_barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Broadband</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_8_barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>mobile_data</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Mobile Data</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_9_barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_9_barriers_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_9_barriers_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_11_internet_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_11_internet_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question_11_internet_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question_12_internet_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question_12_internet_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_12_internet_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_13_devices_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_13_devices_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_13_devices_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_14_devices_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_14_devices_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_14_devices_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_19_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_19_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_19_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_20_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_20_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_20_barriers_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_21_device_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_21_device_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>question_21_device_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>question_22_device_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>question_22_device_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question_22_device_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>question_23_access_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question_23_access_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>question_23_access_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>question_24_access_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>question_24_access_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>question_24_access_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
